--- a/registration_forms/019_open_source_curriculum_testing_registration--registration_forms.xlsx
+++ b/registration_forms/019_open_source_curriculum_testing_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1138,8 +1138,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Option A'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Option B'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Option C'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option_d'}</t>
+          <t>option_d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Option D'}</t>
+          <t>Option D</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_4.1}</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 4.1}</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 1.1}</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 2.1}</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 3.1}</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_4.1}</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 4.1}</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
